--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -166,7 +166,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -483,7 +483,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>100000</v>
+        <v>100010</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>20</v>
@@ -531,7 +531,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>100000</v>
+        <v>100010</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>20</v>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -46,16 +46,16 @@
     <t xml:space="preserve">jsonUnlocks</t>
   </si>
   <si>
-    <t xml:space="preserve">Bow </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannon </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrow </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gun</t>
+    <t xml:space="preserve">Blunderbuss </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20004</t>
   </si>
 </sst>
 </file>
@@ -423,12 +423,12 @@
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.45"/>
@@ -477,13 +477,13 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
-        <v>2001</v>
+        <v>20001</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>100010</v>
+        <v>120010</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>20</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
-        <v>2002</v>
+        <v>20002</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>100010</v>
+        <v>120020</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>20</v>
@@ -525,13 +525,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
-        <v>2003</v>
+        <v>20003</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>100010</v>
+        <v>120030</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>20</v>
@@ -549,13 +549,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
-        <v>2010</v>
+        <v>20004</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>100010</v>
+        <v>120040</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>20</v>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Blunderbuss </t>
   </si>
   <si>
-    <t xml:space="preserve">20002</t>
+    <t xml:space="preserve">Double Barrel </t>
   </si>
   <si>
     <t xml:space="preserve">20003</t>
@@ -145,7 +145,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -167,6 +167,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,7 +427,7 @@
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.69"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.18"/>
@@ -503,7 +507,7 @@
       <c r="A3" s="2" t="n">
         <v>20002</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="n">

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -145,7 +145,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -167,10 +167,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -507,14 +503,14 @@
       <c r="A3" s="2" t="n">
         <v>20002</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>120020</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>6</v>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Double Barrel </t>
   </si>
   <si>
-    <t xml:space="preserve">20003</t>
+    <t xml:space="preserve">Brick</t>
   </si>
   <si>
     <t xml:space="preserve">20004</t>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -424,7 +424,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.52"/>
@@ -477,13 +477,13 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
-        <v>20001</v>
+        <v>2001</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>120010</v>
+        <v>2001</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>20</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
-        <v>20002</v>
+        <v>2002</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>120020</v>
+        <v>2002</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>12</v>
@@ -525,13 +525,13 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
-        <v>20003</v>
+        <v>2003</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>120030</v>
+        <v>2003</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>20</v>
@@ -549,13 +549,13 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
-        <v>20004</v>
+        <v>2004</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>120040</v>
+        <v>2004</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>20</v>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Brick</t>
   </si>
   <si>
-    <t xml:space="preserve">20004</t>
+    <t xml:space="preserve">Ghost Flint</t>
   </si>
 </sst>
 </file>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B028DFB-FAA7-4BD0-9CCD-6DDB10C080E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC8C12F-BBB2-4B1E-8A2E-5CD116072329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4776" yWindow="6204" windowWidth="17280" windowHeight="6624" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="4752" windowWidth="17280" windowHeight="6624" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="weapons" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>skillId</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>path</t>
+  </si>
+  <si>
+    <t>1001 Weapon</t>
   </si>
 </sst>
 </file>
@@ -442,7 +445,9 @@
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="D2">
         <v>100001</v>
       </c>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC8C12F-BBB2-4B1E-8A2E-5CD116072329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F8B390-B529-459C-9F45-5DFF4251445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="4752" windowWidth="17280" windowHeight="6624" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="weapons" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>skillId</t>
   </si>
@@ -42,29 +42,80 @@
     <t>priceBonusLevel</t>
   </si>
   <si>
-    <t>jsonUnlocks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blunderbuss </t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>path</t>
   </si>
   <si>
-    <t>1001 Weapon</t>
+    <t>weaponId</t>
+  </si>
+  <si>
+    <t>weaponName</t>
+  </si>
+  <si>
+    <t>Wooden Sword</t>
+  </si>
+  <si>
+    <t>Iron Sword</t>
+  </si>
+  <si>
+    <t>Bronze Axe</t>
+  </si>
+  <si>
+    <t>Hunter Bow</t>
+  </si>
+  <si>
+    <t>Steel Sword</t>
+  </si>
+  <si>
+    <t>War Axe</t>
+  </si>
+  <si>
+    <t>Long Bow</t>
+  </si>
+  <si>
+    <t>Knight Blade</t>
+  </si>
+  <si>
+    <t>Battle Hammer</t>
+  </si>
+  <si>
+    <t>Assassin Dagger</t>
+  </si>
+  <si>
+    <t>Bronze Spear</t>
+  </si>
+  <si>
+    <t>Silver Spear</t>
+  </si>
+  <si>
+    <t>Knight Sword</t>
+  </si>
+  <si>
+    <t>Hunter Crossbow</t>
+  </si>
+  <si>
+    <t>Flame Blade</t>
+  </si>
+  <si>
+    <t>Ice Blade</t>
+  </si>
+  <si>
+    <t>Thunder Hammer</t>
+  </si>
+  <si>
+    <t>Dragon Spear</t>
+  </si>
+  <si>
+    <t>Phoenix Bow</t>
+  </si>
+  <si>
+    <t>Demon Slayer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +137,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -95,10 +152,30 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -107,16 +184,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -379,89 +471,468 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="20.77734375" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="18.77734375" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" customWidth="1"/>
-    <col min="17" max="17" width="12.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" style="6"/>
+    <col min="5" max="16384" width="15.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" s="8" t="str">
+        <f>_xlfn.CONCAT(A2, " Weapon")</f>
+        <v>1001 Weapon</v>
+      </c>
+      <c r="D2" s="7">
+        <v>3001</v>
+      </c>
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="C3" s="8" t="str">
+        <f t="shared" ref="C3:C21" si="0">_xlfn.CONCAT(A3, " Weapon")</f>
+        <v>1002 Weapon</v>
+      </c>
+      <c r="D3" s="7">
+        <v>3002</v>
+      </c>
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F3" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1003 Weapon</v>
+      </c>
+      <c r="D4" s="7">
+        <v>3003</v>
+      </c>
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1004 Weapon</v>
+      </c>
+      <c r="D5" s="7">
+        <v>3004</v>
+      </c>
+      <c r="E5" s="7">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="F5" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1005 Weapon</v>
+      </c>
+      <c r="D6" s="7">
+        <v>3005</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1006 Weapon</v>
+      </c>
+      <c r="D7" s="7">
+        <v>3006</v>
+      </c>
+      <c r="E7" s="7">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="F7" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1007 Weapon</v>
+      </c>
+      <c r="D8" s="7">
+        <v>3007</v>
+      </c>
+      <c r="E8" s="7">
         <v>5</v>
       </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-    </row>
-    <row r="2" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="F8" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1008 Weapon</v>
+      </c>
+      <c r="D9" s="7">
+        <v>3008</v>
+      </c>
+      <c r="E9" s="7">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F9" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1009 Weapon</v>
+      </c>
+      <c r="D10" s="7">
+        <v>3009</v>
+      </c>
+      <c r="E10" s="7">
+        <v>7</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1010 Weapon</v>
+      </c>
+      <c r="D11" s="7">
+        <v>3010</v>
+      </c>
+      <c r="E11" s="7">
+        <v>8</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1011 Weapon</v>
+      </c>
+      <c r="D12" s="7">
+        <v>3011</v>
+      </c>
+      <c r="E12" s="7">
+        <v>9</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1012 Weapon</v>
+      </c>
+      <c r="D13" s="7">
+        <v>3012</v>
+      </c>
+      <c r="E13" s="7">
         <v>10</v>
       </c>
-      <c r="D2">
-        <v>100001</v>
-      </c>
-      <c r="E2">
+      <c r="F13" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>1013</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="C14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1013 Weapon</v>
+      </c>
+      <c r="D14" s="7">
+        <v>3013</v>
+      </c>
+      <c r="E14" s="7">
+        <v>11</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>1014</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1014 Weapon</v>
+      </c>
+      <c r="D15" s="7">
+        <v>3014</v>
+      </c>
+      <c r="E15" s="7">
+        <v>12</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>1015</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1015 Weapon</v>
+      </c>
+      <c r="D16" s="7">
+        <v>3015</v>
+      </c>
+      <c r="E16" s="7">
+        <v>13</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="7">
+        <v>1016</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1016 Weapon</v>
+      </c>
+      <c r="D17" s="7">
+        <v>3016</v>
+      </c>
+      <c r="E17" s="7">
+        <v>14</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7">
+        <v>1017</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1017 Weapon</v>
+      </c>
+      <c r="D18" s="7">
+        <v>3017</v>
+      </c>
+      <c r="E18" s="7">
+        <v>15</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7">
+        <v>1018</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1018 Weapon</v>
+      </c>
+      <c r="D19" s="7">
+        <v>3018</v>
+      </c>
+      <c r="E19" s="7">
+        <v>16</v>
+      </c>
+      <c r="F19" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="7">
+        <v>1019</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1019 Weapon</v>
+      </c>
+      <c r="D20" s="7">
+        <v>3019</v>
+      </c>
+      <c r="E20" s="7">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
+        <v>1020</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>1020 Weapon</v>
+      </c>
+      <c r="D21" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E21" s="7">
+        <v>20</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F8B390-B529-459C-9F45-5DFF4251445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1A0BAA-BA05-43B2-AA37-A6944829FD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
   <si>
     <t>skillId</t>
   </si>
@@ -51,64 +51,79 @@
     <t>weaponName</t>
   </si>
   <si>
-    <t>Wooden Sword</t>
-  </si>
-  <si>
-    <t>Iron Sword</t>
-  </si>
-  <si>
-    <t>Bronze Axe</t>
-  </si>
-  <si>
-    <t>Hunter Bow</t>
-  </si>
-  <si>
-    <t>Steel Sword</t>
-  </si>
-  <si>
-    <t>War Axe</t>
-  </si>
-  <si>
-    <t>Long Bow</t>
-  </si>
-  <si>
-    <t>Knight Blade</t>
-  </si>
-  <si>
-    <t>Battle Hammer</t>
-  </si>
-  <si>
-    <t>Assassin Dagger</t>
-  </si>
-  <si>
-    <t>Bronze Spear</t>
-  </si>
-  <si>
-    <t>Silver Spear</t>
-  </si>
-  <si>
-    <t>Knight Sword</t>
-  </si>
-  <si>
-    <t>Hunter Crossbow</t>
-  </si>
-  <si>
-    <t>Flame Blade</t>
-  </si>
-  <si>
-    <t>Ice Blade</t>
-  </si>
-  <si>
-    <t>Thunder Hammer</t>
-  </si>
-  <si>
-    <t>Dragon Spear</t>
-  </si>
-  <si>
-    <t>Phoenix Bow</t>
-  </si>
-  <si>
-    <t>Demon Slayer</t>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>Captain's Sword</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>Blade</t>
+  </si>
+  <si>
+    <t>Blunt</t>
+  </si>
+  <si>
+    <t>Unarmed</t>
+  </si>
+  <si>
+    <t>Explosive</t>
+  </si>
+  <si>
+    <t>Chopper</t>
+  </si>
+  <si>
+    <t>Chainsaw</t>
+  </si>
+  <si>
+    <t>Brick</t>
+  </si>
+  <si>
+    <t>Rock</t>
+  </si>
+  <si>
+    <t>Spoon</t>
+  </si>
+  <si>
+    <t>Hammer</t>
+  </si>
+  <si>
+    <t>Claw</t>
+  </si>
+  <si>
+    <t>Fist</t>
+  </si>
+  <si>
+    <t>Hand</t>
+  </si>
+  <si>
+    <t>Plank</t>
+  </si>
+  <si>
+    <t>Shredder</t>
+  </si>
+  <si>
+    <t>Fireball</t>
+  </si>
+  <si>
+    <t>Circular Saw</t>
+  </si>
+  <si>
+    <t>Spiky Shield</t>
+  </si>
+  <si>
+    <t>Flaming Brass Knuckles</t>
+  </si>
+  <si>
+    <t>Power Fist</t>
+  </si>
+  <si>
+    <t>Grenade Launcher</t>
+  </si>
+  <si>
+    <t>Rocket Launcher</t>
   </si>
 </sst>
 </file>
@@ -471,42 +486,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.90625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" style="6"/>
-    <col min="5" max="16384" width="15.6328125" style="1"/>
+    <col min="1" max="2" width="10.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="6"/>
+    <col min="6" max="16384" width="15.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -514,424 +531,485 @@
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
-    </row>
-    <row r="2" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="Q1" s="3"/>
+    </row>
+    <row r="2" spans="1:17" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>1001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="8" t="str">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8" t="str">
         <f>_xlfn.CONCAT(A2, " Weapon")</f>
         <v>1001 Weapon</v>
       </c>
-      <c r="D2" s="7">
+      <c r="E2" s="7">
         <v>3001</v>
       </c>
-      <c r="E2" s="7">
+      <c r="F2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="7">
+      <c r="G2" s="7">
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>1002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="8" t="str">
-        <f t="shared" ref="C3:C21" si="0">_xlfn.CONCAT(A3, " Weapon")</f>
+        <v>11</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8" t="str">
+        <f t="shared" ref="D3:D21" si="0">_xlfn.CONCAT(A3, " Weapon")</f>
         <v>1002 Weapon</v>
       </c>
-      <c r="D3" s="7">
+      <c r="E3" s="7">
         <v>3002</v>
       </c>
-      <c r="E3" s="7">
+      <c r="F3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="7">
+      <c r="G3" s="7">
         <v>0.03</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>1003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="8" t="str">
+        <v>11</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1003 Weapon</v>
       </c>
-      <c r="D4" s="7">
+      <c r="E4" s="7">
         <v>3003</v>
       </c>
-      <c r="E4" s="7">
+      <c r="F4" s="7">
         <v>2</v>
       </c>
-      <c r="F4" s="7">
+      <c r="G4" s="7">
         <v>0.03</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>1004</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="8" t="str">
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1004 Weapon</v>
       </c>
-      <c r="D5" s="7">
+      <c r="E5" s="7">
         <v>3004</v>
       </c>
-      <c r="E5" s="7">
+      <c r="F5" s="7">
         <v>3</v>
       </c>
-      <c r="F5" s="7">
+      <c r="G5" s="7">
         <v>0.04</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>1005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8" t="str">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1005 Weapon</v>
       </c>
-      <c r="D6" s="7">
+      <c r="E6" s="7">
         <v>3005</v>
       </c>
-      <c r="E6" s="7">
+      <c r="F6" s="7">
         <v>3</v>
       </c>
-      <c r="F6" s="7">
+      <c r="G6" s="7">
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>1006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="8" t="str">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1006 Weapon</v>
       </c>
-      <c r="D7" s="7">
+      <c r="E7" s="7">
         <v>3006</v>
       </c>
-      <c r="E7" s="7">
+      <c r="F7" s="7">
         <v>4</v>
       </c>
-      <c r="F7" s="7">
+      <c r="G7" s="7">
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>1007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="8" t="str">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1007 Weapon</v>
       </c>
-      <c r="D8" s="7">
+      <c r="E8" s="7">
         <v>3007</v>
       </c>
-      <c r="E8" s="7">
+      <c r="F8" s="7">
         <v>5</v>
       </c>
-      <c r="F8" s="7">
+      <c r="G8" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>1008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="8" t="str">
+        <v>12</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1008 Weapon</v>
       </c>
-      <c r="D9" s="7">
+      <c r="E9" s="7">
         <v>3008</v>
       </c>
-      <c r="E9" s="7">
+      <c r="F9" s="7">
         <v>6</v>
       </c>
-      <c r="F9" s="7">
+      <c r="G9" s="7">
         <v>0.08</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>1009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="8" t="str">
+        <v>12</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1009 Weapon</v>
       </c>
-      <c r="D10" s="7">
+      <c r="E10" s="7">
         <v>3009</v>
       </c>
-      <c r="E10" s="7">
+      <c r="F10" s="7">
         <v>7</v>
       </c>
-      <c r="F10" s="7">
+      <c r="G10" s="7">
         <v>0.09</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>1010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="8" t="str">
+        <v>12</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1010 Weapon</v>
       </c>
-      <c r="D11" s="7">
+      <c r="E11" s="7">
         <v>3010</v>
       </c>
-      <c r="E11" s="7">
+      <c r="F11" s="7">
         <v>8</v>
       </c>
-      <c r="F11" s="7">
+      <c r="G11" s="7">
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>1011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8" t="str">
+        <v>13</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1011 Weapon</v>
       </c>
-      <c r="D12" s="7">
+      <c r="E12" s="7">
         <v>3011</v>
       </c>
-      <c r="E12" s="7">
+      <c r="F12" s="7">
         <v>9</v>
       </c>
-      <c r="F12" s="7">
+      <c r="G12" s="7">
         <v>0.11</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>1012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="8" t="str">
+        <v>13</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1012 Weapon</v>
       </c>
-      <c r="D13" s="7">
+      <c r="E13" s="7">
         <v>3012</v>
       </c>
-      <c r="E13" s="7">
+      <c r="F13" s="7">
         <v>10</v>
       </c>
-      <c r="F13" s="7">
+      <c r="G13" s="7">
         <v>0.12</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>1013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="8" t="str">
+        <v>13</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1013 Weapon</v>
       </c>
-      <c r="D14" s="7">
+      <c r="E14" s="7">
         <v>3013</v>
       </c>
-      <c r="E14" s="7">
+      <c r="F14" s="7">
         <v>11</v>
       </c>
-      <c r="F14" s="7">
+      <c r="G14" s="7">
         <v>0.13</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>1014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="8" t="str">
+        <v>13</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1014 Weapon</v>
       </c>
-      <c r="D15" s="7">
+      <c r="E15" s="7">
         <v>3014</v>
       </c>
-      <c r="E15" s="7">
+      <c r="F15" s="7">
         <v>12</v>
       </c>
-      <c r="F15" s="7">
+      <c r="G15" s="7">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>1015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="8" t="str">
+        <v>13</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1015 Weapon</v>
       </c>
-      <c r="D16" s="7">
+      <c r="E16" s="7">
         <v>3015</v>
       </c>
-      <c r="E16" s="7">
+      <c r="F16" s="7">
         <v>13</v>
       </c>
-      <c r="F16" s="7">
+      <c r="G16" s="7">
         <v>0.15</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>1016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="8" t="str">
+        <v>14</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1016 Weapon</v>
       </c>
-      <c r="D17" s="7">
+      <c r="E17" s="7">
         <v>3016</v>
       </c>
-      <c r="E17" s="7">
+      <c r="F17" s="7">
         <v>14</v>
       </c>
-      <c r="F17" s="7">
+      <c r="G17" s="7">
         <v>0.16</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>1017</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="8" t="str">
+        <v>14</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1017 Weapon</v>
       </c>
-      <c r="D18" s="7">
+      <c r="E18" s="7">
         <v>3017</v>
       </c>
-      <c r="E18" s="7">
+      <c r="F18" s="7">
         <v>15</v>
       </c>
-      <c r="F18" s="7">
+      <c r="G18" s="7">
         <v>0.18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>1018</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="8" t="str">
+        <v>14</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1018 Weapon</v>
       </c>
-      <c r="D19" s="7">
+      <c r="E19" s="7">
         <v>3018</v>
       </c>
-      <c r="E19" s="7">
+      <c r="F19" s="7">
         <v>16</v>
       </c>
-      <c r="F19" s="7">
+      <c r="G19" s="7">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>1019</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="8" t="str">
+        <v>14</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1019 Weapon</v>
       </c>
-      <c r="D20" s="7">
+      <c r="E20" s="7">
         <v>3019</v>
       </c>
-      <c r="E20" s="7">
+      <c r="F20" s="7">
         <v>18</v>
       </c>
-      <c r="F20" s="7">
+      <c r="G20" s="7">
         <v>0.22</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>1020</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="8" t="str">
+        <v>14</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="8" t="str">
         <f t="shared" si="0"/>
         <v>1020 Weapon</v>
       </c>
-      <c r="D21" s="7">
+      <c r="E21" s="7">
         <v>3020</v>
       </c>
-      <c r="E21" s="7">
+      <c r="F21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="7">
+      <c r="G21" s="7">
         <v>0.25</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1A0BAA-BA05-43B2-AA37-A6944829FD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF6E160-AF66-4058-B3EC-B293BA45F005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -195,11 +195,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -223,6 +232,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -550,11 +565,11 @@
       <c r="E2" s="7">
         <v>3001</v>
       </c>
-      <c r="F2" s="7">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0.02</v>
+      <c r="F2" s="9">
+        <v>8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.08</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -574,11 +589,11 @@
       <c r="E3" s="7">
         <v>3002</v>
       </c>
-      <c r="F3" s="7">
-        <v>2</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0.03</v>
+      <c r="F3" s="9">
+        <v>10</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -598,11 +613,11 @@
       <c r="E4" s="7">
         <v>3003</v>
       </c>
-      <c r="F4" s="7">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0.03</v>
+      <c r="F4" s="9">
+        <v>9</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.09</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -622,11 +637,11 @@
       <c r="E5" s="7">
         <v>3004</v>
       </c>
-      <c r="F5" s="7">
-        <v>3</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0.04</v>
+      <c r="F5" s="9">
+        <v>14</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.12</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -646,11 +661,11 @@
       <c r="E6" s="7">
         <v>3005</v>
       </c>
-      <c r="F6" s="7">
-        <v>3</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0.05</v>
+      <c r="F6" s="9">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -670,11 +685,11 @@
       <c r="E7" s="7">
         <v>3006</v>
       </c>
-      <c r="F7" s="7">
-        <v>4</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.06</v>
+      <c r="F7" s="9">
+        <v>7</v>
+      </c>
+      <c r="G7" s="10">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -694,11 +709,11 @@
       <c r="E8" s="7">
         <v>3007</v>
       </c>
-      <c r="F8" s="7">
-        <v>5</v>
-      </c>
-      <c r="G8" s="7">
-        <v>7.0000000000000007E-2</v>
+      <c r="F8" s="9">
+        <v>10</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.09</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -718,11 +733,11 @@
       <c r="E9" s="7">
         <v>3008</v>
       </c>
-      <c r="F9" s="7">
-        <v>6</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.08</v>
+      <c r="F9" s="9">
+        <v>13</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -742,11 +757,11 @@
       <c r="E10" s="7">
         <v>3009</v>
       </c>
-      <c r="F10" s="7">
-        <v>7</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0.09</v>
+      <c r="F10" s="9">
+        <v>8</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.08</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -766,11 +781,11 @@
       <c r="E11" s="7">
         <v>3010</v>
       </c>
-      <c r="F11" s="7">
-        <v>8</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0.1</v>
+      <c r="F11" s="9">
+        <v>18</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -790,11 +805,11 @@
       <c r="E12" s="7">
         <v>3011</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="9">
         <v>9</v>
       </c>
-      <c r="G12" s="7">
-        <v>0.11</v>
+      <c r="G12" s="10">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -814,11 +829,11 @@
       <c r="E13" s="7">
         <v>3012</v>
       </c>
-      <c r="F13" s="7">
-        <v>10</v>
-      </c>
-      <c r="G13" s="7">
-        <v>0.12</v>
+      <c r="F13" s="9">
+        <v>7</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0.08</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -838,11 +853,11 @@
       <c r="E14" s="7">
         <v>3013</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="9">
         <v>11</v>
       </c>
-      <c r="G14" s="7">
-        <v>0.13</v>
+      <c r="G14" s="10">
+        <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -862,11 +877,11 @@
       <c r="E15" s="7">
         <v>3014</v>
       </c>
-      <c r="F15" s="7">
-        <v>12</v>
-      </c>
-      <c r="G15" s="7">
-        <v>0.14000000000000001</v>
+      <c r="F15" s="9">
+        <v>8</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0.09</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -886,11 +901,11 @@
       <c r="E16" s="7">
         <v>3015</v>
       </c>
-      <c r="F16" s="7">
-        <v>13</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0.15</v>
+      <c r="F16" s="9">
+        <v>20</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0.16</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -910,11 +925,11 @@
       <c r="E17" s="7">
         <v>3016</v>
       </c>
-      <c r="F17" s="7">
-        <v>14</v>
-      </c>
-      <c r="G17" s="7">
-        <v>0.16</v>
+      <c r="F17" s="9">
+        <v>10</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.08</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -934,11 +949,11 @@
       <c r="E18" s="7">
         <v>3017</v>
       </c>
-      <c r="F18" s="7">
-        <v>15</v>
-      </c>
-      <c r="G18" s="7">
-        <v>0.18</v>
+      <c r="F18" s="9">
+        <v>16</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0.12</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -958,11 +973,11 @@
       <c r="E19" s="7">
         <v>3018</v>
       </c>
-      <c r="F19" s="7">
-        <v>16</v>
-      </c>
-      <c r="G19" s="7">
-        <v>0.2</v>
+      <c r="F19" s="9">
+        <v>18</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0.13</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -982,11 +997,11 @@
       <c r="E20" s="7">
         <v>3019</v>
       </c>
-      <c r="F20" s="7">
-        <v>18</v>
-      </c>
-      <c r="G20" s="7">
-        <v>0.22</v>
+      <c r="F20" s="9">
+        <v>28</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0.18</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -1006,11 +1021,11 @@
       <c r="E21" s="7">
         <v>3020</v>
       </c>
-      <c r="F21" s="7">
-        <v>20</v>
-      </c>
-      <c r="G21" s="7">
-        <v>0.25</v>
+      <c r="F21" s="9">
+        <v>35</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/WeaponConfig.xlsx
+++ b/light_fight/Assets/Excels/WeaponConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF6E160-AF66-4058-B3EC-B293BA45F005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3A0C41-B0F1-4784-838F-BB7972E39EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>skillId</t>
   </si>
@@ -124,6 +124,12 @@
   </si>
   <si>
     <t>Rocket Launcher</t>
+  </si>
+  <si>
+    <t>skillCooldown</t>
+  </si>
+  <si>
+    <t>attackRange</t>
   </si>
 </sst>
 </file>
@@ -167,7 +173,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -177,17 +183,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -222,23 +217,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,17 +496,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultColWidth="15.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.6328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.90625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="6"/>
-    <col min="6" max="16384" width="15.6328125" style="1"/>
+    <col min="5" max="6" width="15.6328125" style="9"/>
+    <col min="7" max="7" width="15.6328125" style="4"/>
+    <col min="8" max="16384" width="15.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -524,507 +520,633 @@
       <c r="D1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
-    </row>
-    <row r="2" spans="1:17" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+    </row>
+    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
         <v>1001</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="6" t="str">
         <f>_xlfn.CONCAT(A2, " Weapon")</f>
         <v>1001 Weapon</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>3001</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G2" s="6">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5">
         <v>8</v>
       </c>
-      <c r="G2" s="10">
+      <c r="I2" s="5">
         <v>0.08</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7">
+    <row r="3" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
         <v>1002</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8" t="str">
+      <c r="D3" s="6" t="str">
         <f t="shared" ref="D3:D21" si="0">_xlfn.CONCAT(A3, " Weapon")</f>
         <v>1002 Weapon</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>3002</v>
       </c>
-      <c r="F3" s="9">
-        <v>10</v>
-      </c>
-      <c r="G3" s="10">
+      <c r="F3" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G3" s="6">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
+    <row r="4" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
         <v>1003</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="8" t="str">
+      <c r="D4" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1003 Weapon</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>3003</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G4" s="6">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
         <v>9</v>
       </c>
-      <c r="G4" s="10">
+      <c r="I4" s="5">
         <v>0.09</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7">
+    <row r="5" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
         <v>1004</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="8" t="str">
+      <c r="D5" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1004 Weapon</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>3004</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="6">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
         <v>14</v>
       </c>
-      <c r="G5" s="10">
+      <c r="I5" s="5">
         <v>0.12</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
+    <row r="6" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <v>1005</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="8" t="str">
+      <c r="D6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1005 Weapon</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>3005</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="6">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5">
         <v>16</v>
       </c>
-      <c r="G6" s="10">
+      <c r="I6" s="5">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
+    <row r="7" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
         <v>1006</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="8" t="str">
+      <c r="D7" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1006 Weapon</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>3006</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>10</v>
+      </c>
+      <c r="H7" s="5">
         <v>7</v>
       </c>
-      <c r="G7" s="10">
+      <c r="I7" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
+    <row r="8" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
         <v>1007</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="8" t="str">
+      <c r="D8" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1007 Weapon</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>3007</v>
       </c>
-      <c r="F8" s="9">
-        <v>10</v>
-      </c>
-      <c r="G8" s="10">
+      <c r="F8" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="6">
+        <v>10</v>
+      </c>
+      <c r="H8" s="5">
+        <v>10</v>
+      </c>
+      <c r="I8" s="5">
         <v>0.09</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
+    <row r="9" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
         <v>1008</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="8" t="str">
+      <c r="D9" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1008 Weapon</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>3008</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="6">
+        <v>10</v>
+      </c>
+      <c r="H9" s="5">
         <v>13</v>
       </c>
-      <c r="G9" s="10">
+      <c r="I9" s="5">
         <v>0.11</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
+    <row r="10" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
         <v>1009</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="8" t="str">
+      <c r="D10" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1009 Weapon</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>3009</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G10" s="6">
+        <v>10</v>
+      </c>
+      <c r="H10" s="5">
         <v>8</v>
       </c>
-      <c r="G10" s="10">
+      <c r="I10" s="5">
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
+    <row r="11" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
         <v>1010</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="8" t="str">
+      <c r="D11" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1010 Weapon</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>3010</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="6">
+        <v>10</v>
+      </c>
+      <c r="H11" s="5">
         <v>18</v>
       </c>
-      <c r="G11" s="10">
+      <c r="I11" s="5">
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
+    <row r="12" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
         <v>1011</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="8" t="str">
+      <c r="D12" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1011 Weapon</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>3011</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G12" s="6">
+        <v>10</v>
+      </c>
+      <c r="H12" s="5">
         <v>9</v>
       </c>
-      <c r="G12" s="10">
+      <c r="I12" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7">
+    <row r="13" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
         <v>1012</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="8" t="str">
+      <c r="D13" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1012 Weapon</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>3012</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G13" s="6">
+        <v>10</v>
+      </c>
+      <c r="H13" s="5">
         <v>7</v>
       </c>
-      <c r="G13" s="10">
+      <c r="I13" s="5">
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
+    <row r="14" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
         <v>1013</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="8" t="str">
+      <c r="D14" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1013 Weapon</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>3013</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="6">
+        <v>10</v>
+      </c>
+      <c r="H14" s="5">
         <v>11</v>
       </c>
-      <c r="G14" s="10">
+      <c r="I14" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7">
+    <row r="15" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
         <v>1014</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="8" t="str">
+      <c r="D15" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1014 Weapon</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>3014</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="6">
+        <v>10</v>
+      </c>
+      <c r="H15" s="5">
         <v>8</v>
       </c>
-      <c r="G15" s="10">
+      <c r="I15" s="5">
         <v>0.09</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
+    <row r="16" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
         <v>1015</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="8" t="str">
+      <c r="D16" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1015 Weapon</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>3015</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G16" s="6">
+        <v>10</v>
+      </c>
+      <c r="H16" s="5">
         <v>20</v>
       </c>
-      <c r="G16" s="10">
+      <c r="I16" s="5">
         <v>0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
+    <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
         <v>1016</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="8" t="str">
+      <c r="D17" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1016 Weapon</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>3016</v>
       </c>
-      <c r="F17" s="9">
-        <v>10</v>
-      </c>
-      <c r="G17" s="10">
+      <c r="F17" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G17" s="6">
+        <v>10</v>
+      </c>
+      <c r="H17" s="5">
+        <v>10</v>
+      </c>
+      <c r="I17" s="5">
         <v>0.08</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
+    <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
         <v>1017</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="8" t="str">
+      <c r="D18" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1017 Weapon</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>3017</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="6">
+        <v>10</v>
+      </c>
+      <c r="H18" s="5">
         <v>16</v>
       </c>
-      <c r="G18" s="10">
+      <c r="I18" s="5">
         <v>0.12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7">
+    <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
         <v>1018</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="8" t="str">
+      <c r="D19" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1018 Weapon</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <v>3018</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="6">
+        <v>10</v>
+      </c>
+      <c r="H19" s="5">
         <v>18</v>
       </c>
-      <c r="G19" s="10">
+      <c r="I19" s="5">
         <v>0.13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
+    <row r="20" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
         <v>1019</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="8" t="str">
+      <c r="D20" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1019 Weapon</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>3019</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G20" s="6">
+        <v>10</v>
+      </c>
+      <c r="H20" s="5">
         <v>28</v>
       </c>
-      <c r="G20" s="10">
+      <c r="I20" s="5">
         <v>0.18</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="7">
+    <row r="21" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
         <v>1020</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="8" t="str">
+      <c r="D21" s="6" t="str">
         <f t="shared" si="0"/>
         <v>1020 Weapon</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <v>3020</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="6">
+        <v>10</v>
+      </c>
+      <c r="H21" s="5">
         <v>35</v>
       </c>
-      <c r="G21" s="10">
+      <c r="I21" s="5">
         <v>0.22</v>
       </c>
     </row>
